--- a/erp-server/erp-server-wms/src/main/resources/excel/packingDetailExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/packingDetailExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>装箱任务</t>
   </si>
@@ -40,6 +40,9 @@
     <t>单据类型</t>
   </si>
   <si>
+    <t>箱号</t>
+  </si>
+  <si>
     <t>装箱状态</t>
   </si>
   <si>
@@ -71,6 +74,9 @@
   </si>
   <si>
     <t>{.sourceTypeName}</t>
+  </si>
+  <si>
+    <t>{.boxNo}</t>
   </si>
   <si>
     <t>{.packingTotalStatusName}</t>
@@ -1096,31 +1102,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
     <col min="2" max="2" width="19.125" customWidth="1"/>
     <col min="3" max="3" width="16.5" customWidth="1"/>
-    <col min="4" max="4" width="18.5" customWidth="1"/>
-    <col min="5" max="5" width="16.5" customWidth="1"/>
-    <col min="6" max="6" width="20.5" customWidth="1"/>
-    <col min="7" max="7" width="13.125" customWidth="1"/>
-    <col min="8" max="8" width="12.375" customWidth="1"/>
-    <col min="9" max="9" width="18.5" customWidth="1"/>
-    <col min="10" max="10" width="24.75" customWidth="1"/>
-    <col min="11" max="11" width="14.875" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
-    <col min="13" max="13" width="36.375" customWidth="1"/>
-    <col min="14" max="14" width="10.375" customWidth="1"/>
-    <col min="16" max="16" width="8.875" customWidth="1"/>
-    <col min="17" max="17" width="31.25" customWidth="1"/>
-    <col min="19" max="19" width="17.375" customWidth="1"/>
-    <col min="21" max="21" width="9.375" customWidth="1"/>
-    <col min="22" max="22" width="18" customWidth="1"/>
+    <col min="4" max="5" width="18.5" customWidth="1"/>
+    <col min="6" max="6" width="16.5" customWidth="1"/>
+    <col min="7" max="7" width="20.5" customWidth="1"/>
+    <col min="8" max="8" width="13.125" customWidth="1"/>
+    <col min="9" max="9" width="12.375" customWidth="1"/>
+    <col min="10" max="10" width="18.5" customWidth="1"/>
+    <col min="11" max="11" width="24.75" customWidth="1"/>
+    <col min="12" max="12" width="14.875" customWidth="1"/>
+    <col min="13" max="13" width="9" customWidth="1"/>
+    <col min="14" max="14" width="36.375" customWidth="1"/>
+    <col min="15" max="15" width="10.375" customWidth="1"/>
+    <col min="17" max="17" width="8.875" customWidth="1"/>
+    <col min="18" max="18" width="31.25" customWidth="1"/>
+    <col min="20" max="20" width="17.375" customWidth="1"/>
+    <col min="22" max="22" width="9.375" customWidth="1"/>
+    <col min="23" max="23" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1145,7 +1151,7 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="4" t="s">
@@ -1154,40 +1160,46 @@
       <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:11">
+    <row r="2" s="1" customFormat="1" spans="1:12">
       <c r="A2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
